--- a/public/samples/ko/sample1.xlsx
+++ b/public/samples/ko/sample1.xlsx
@@ -492,7 +492,7 @@
         <v>학업 성취도</v>
       </c>
       <c r="E2" s="2" t="str">
-        <v>교우 관계</v>
+        <v>교우 관계 지원</v>
       </c>
       <c r="F2" s="2" t="str">
         <v>특수교육 대상</v>
@@ -521,7 +521,7 @@
         <v>73</v>
       </c>
       <c r="E3" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F3" s="2" t="str">
         <v/>
@@ -550,7 +550,7 @@
         <v>67</v>
       </c>
       <c r="E4" s="2" t="str">
-        <v>원만</v>
+        <v/>
       </c>
       <c r="F4" s="2" t="str">
         <v/>
@@ -579,7 +579,7 @@
         <v>79</v>
       </c>
       <c r="E5" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F5" s="2" t="str">
         <v/>
@@ -608,7 +608,7 @@
         <v>72</v>
       </c>
       <c r="E6" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F6" s="2" t="str">
         <v/>
@@ -637,7 +637,7 @@
         <v>78</v>
       </c>
       <c r="E7" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F7" s="2" t="str">
         <v/>
@@ -666,7 +666,7 @@
         <v>68</v>
       </c>
       <c r="E8" s="2" t="str">
-        <v>원만</v>
+        <v/>
       </c>
       <c r="F8" s="2" t="str">
         <v/>
@@ -695,7 +695,7 @@
         <v>77</v>
       </c>
       <c r="E9" s="2" t="str">
-        <v>지원 필요</v>
+        <v/>
       </c>
       <c r="F9" s="2" t="str">
         <v/>
@@ -724,7 +724,7 @@
         <v>83</v>
       </c>
       <c r="E10" s="2" t="str">
-        <v>원만</v>
+        <v>✓</v>
       </c>
       <c r="F10" s="2" t="str">
         <v>✓</v>
@@ -753,7 +753,7 @@
         <v>86</v>
       </c>
       <c r="E11" s="2" t="str">
-        <v>원만</v>
+        <v/>
       </c>
       <c r="F11" s="2" t="str">
         <v/>
@@ -782,7 +782,7 @@
         <v>71</v>
       </c>
       <c r="E12" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F12" s="2" t="str">
         <v/>
@@ -811,7 +811,7 @@
         <v>75</v>
       </c>
       <c r="E13" s="2" t="str">
-        <v>원만</v>
+        <v>✓</v>
       </c>
       <c r="F13" s="2" t="str">
         <v/>
@@ -840,7 +840,7 @@
         <v>88</v>
       </c>
       <c r="E14" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F14" s="2" t="str">
         <v>✓</v>
@@ -869,7 +869,7 @@
         <v>76</v>
       </c>
       <c r="E15" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F15" s="2" t="str">
         <v/>
@@ -898,7 +898,7 @@
         <v>70</v>
       </c>
       <c r="E16" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F16" s="2" t="str">
         <v>✓</v>
@@ -927,7 +927,7 @@
         <v>73</v>
       </c>
       <c r="E17" s="2" t="str">
-        <v>원만</v>
+        <v>✓</v>
       </c>
       <c r="F17" s="2" t="str">
         <v>✓</v>
@@ -956,7 +956,7 @@
         <v>88</v>
       </c>
       <c r="E18" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F18" s="2" t="str">
         <v/>
@@ -985,7 +985,7 @@
         <v>72</v>
       </c>
       <c r="E19" s="2" t="str">
-        <v>원만</v>
+        <v/>
       </c>
       <c r="F19" s="2" t="str">
         <v/>
@@ -1014,7 +1014,7 @@
         <v>74</v>
       </c>
       <c r="E20" s="2" t="str">
-        <v>원만</v>
+        <v/>
       </c>
       <c r="F20" s="2" t="str">
         <v/>
@@ -1043,7 +1043,7 @@
         <v>82</v>
       </c>
       <c r="E21" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F21" s="2" t="str">
         <v/>
@@ -1072,7 +1072,7 @@
         <v>84</v>
       </c>
       <c r="E22" s="2" t="str">
-        <v>원만</v>
+        <v/>
       </c>
       <c r="F22" s="2" t="str">
         <v/>
@@ -1101,7 +1101,7 @@
         <v>71</v>
       </c>
       <c r="E23" s="2" t="str">
-        <v>원만</v>
+        <v/>
       </c>
       <c r="F23" s="2" t="str">
         <v/>
@@ -1130,7 +1130,7 @@
         <v>80</v>
       </c>
       <c r="E24" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F24" s="2" t="str">
         <v/>
@@ -1159,7 +1159,7 @@
         <v>75</v>
       </c>
       <c r="E25" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F25" s="2" t="str">
         <v/>
@@ -1188,7 +1188,7 @@
         <v>85</v>
       </c>
       <c r="E26" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F26" s="2" t="str">
         <v/>
@@ -1217,7 +1217,7 @@
         <v>94</v>
       </c>
       <c r="E27" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F27" s="2" t="str">
         <v/>
@@ -1246,7 +1246,7 @@
         <v>83</v>
       </c>
       <c r="E28" s="2" t="str">
-        <v>지원 필요</v>
+        <v/>
       </c>
       <c r="F28" s="2" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>78</v>
       </c>
       <c r="E29" s="2" t="str">
-        <v>지원 필요</v>
+        <v/>
       </c>
       <c r="F29" s="2" t="str">
         <v>✓</v>
@@ -1304,7 +1304,7 @@
         <v>84</v>
       </c>
       <c r="E30" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F30" s="2" t="str">
         <v/>
@@ -1333,7 +1333,7 @@
         <v>62</v>
       </c>
       <c r="E31" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F31" s="2" t="str">
         <v/>
@@ -1362,7 +1362,7 @@
         <v>75</v>
       </c>
       <c r="E32" s="2" t="str">
-        <v>지원 필요</v>
+        <v/>
       </c>
       <c r="F32" s="2" t="str">
         <v/>
@@ -1391,7 +1391,7 @@
         <v>71</v>
       </c>
       <c r="E33" s="2" t="str">
-        <v>원만</v>
+        <v/>
       </c>
       <c r="F33" s="2" t="str">
         <v/>
@@ -1420,7 +1420,7 @@
         <v>84</v>
       </c>
       <c r="E34" s="2" t="str">
-        <v>원만</v>
+        <v/>
       </c>
       <c r="F34" s="2" t="str">
         <v/>
@@ -1449,7 +1449,7 @@
         <v>72</v>
       </c>
       <c r="E35" s="2" t="str">
-        <v>원만</v>
+        <v/>
       </c>
       <c r="F35" s="2" t="str">
         <v/>
@@ -1478,7 +1478,7 @@
         <v>64</v>
       </c>
       <c r="E36" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F36" s="2" t="str">
         <v/>
@@ -1507,7 +1507,7 @@
         <v>65</v>
       </c>
       <c r="E37" s="2" t="str">
-        <v>원만</v>
+        <v/>
       </c>
       <c r="F37" s="2" t="str">
         <v>✓</v>
@@ -1536,7 +1536,7 @@
         <v>74</v>
       </c>
       <c r="E38" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F38" s="2" t="str">
         <v/>
@@ -1565,7 +1565,7 @@
         <v>73</v>
       </c>
       <c r="E39" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F39" s="2" t="str">
         <v/>
@@ -1594,7 +1594,7 @@
         <v>78</v>
       </c>
       <c r="E40" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F40" s="2" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>67</v>
       </c>
       <c r="E41" s="2" t="str">
-        <v>원만</v>
+        <v>✓</v>
       </c>
       <c r="F41" s="2" t="str">
         <v/>
@@ -1652,7 +1652,7 @@
         <v>73</v>
       </c>
       <c r="E42" s="2" t="str">
-        <v>원만</v>
+        <v/>
       </c>
       <c r="F42" s="2" t="str">
         <v/>
@@ -1681,7 +1681,7 @@
         <v>81</v>
       </c>
       <c r="E43" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F43" s="2" t="str">
         <v/>
@@ -1710,7 +1710,7 @@
         <v>79</v>
       </c>
       <c r="E44" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F44" s="2" t="str">
         <v/>
@@ -1739,7 +1739,7 @@
         <v>81</v>
       </c>
       <c r="E45" s="2" t="str">
-        <v>지원 필요</v>
+        <v/>
       </c>
       <c r="F45" s="2" t="str">
         <v/>
@@ -1768,7 +1768,7 @@
         <v>81</v>
       </c>
       <c r="E46" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F46" s="2" t="str">
         <v/>
@@ -1797,7 +1797,7 @@
         <v>89</v>
       </c>
       <c r="E47" s="2" t="str">
-        <v>원만</v>
+        <v/>
       </c>
       <c r="F47" s="2" t="str">
         <v/>
@@ -1826,7 +1826,7 @@
         <v>74</v>
       </c>
       <c r="E48" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F48" s="2" t="str">
         <v/>
@@ -1855,7 +1855,7 @@
         <v>81</v>
       </c>
       <c r="E49" s="2" t="str">
-        <v>지원 필요</v>
+        <v/>
       </c>
       <c r="F49" s="2" t="str">
         <v/>
@@ -1884,7 +1884,7 @@
         <v>80</v>
       </c>
       <c r="E50" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F50" s="2" t="str">
         <v/>
@@ -1913,7 +1913,7 @@
         <v>78</v>
       </c>
       <c r="E51" s="2" t="str">
-        <v>원만</v>
+        <v/>
       </c>
       <c r="F51" s="2" t="str">
         <v/>
@@ -1942,7 +1942,7 @@
         <v>93</v>
       </c>
       <c r="E52" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F52" s="2" t="str">
         <v>✓</v>
@@ -1971,7 +1971,7 @@
         <v>64</v>
       </c>
       <c r="E53" s="2" t="str">
-        <v>지원 필요</v>
+        <v/>
       </c>
       <c r="F53" s="2" t="str">
         <v/>
@@ -2000,7 +2000,7 @@
         <v>79</v>
       </c>
       <c r="E54" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F54" s="2" t="str">
         <v>✓</v>
@@ -2029,7 +2029,7 @@
         <v>75</v>
       </c>
       <c r="E55" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F55" s="2" t="str">
         <v/>
@@ -2058,7 +2058,7 @@
         <v>84</v>
       </c>
       <c r="E56" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F56" s="2" t="str">
         <v/>
@@ -2087,7 +2087,7 @@
         <v>78</v>
       </c>
       <c r="E57" s="2" t="str">
-        <v>원만</v>
+        <v/>
       </c>
       <c r="F57" s="2" t="str">
         <v/>
@@ -2116,7 +2116,7 @@
         <v>82</v>
       </c>
       <c r="E58" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F58" s="2" t="str">
         <v/>
@@ -2145,7 +2145,7 @@
         <v>93</v>
       </c>
       <c r="E59" s="2" t="str">
-        <v>원만</v>
+        <v>✓</v>
       </c>
       <c r="F59" s="2" t="str">
         <v/>
@@ -2174,7 +2174,7 @@
         <v>87</v>
       </c>
       <c r="E60" s="2" t="str">
-        <v>지원 필요</v>
+        <v/>
       </c>
       <c r="F60" s="2" t="str">
         <v/>
@@ -2203,7 +2203,7 @@
         <v>72</v>
       </c>
       <c r="E61" s="2" t="str">
-        <v>지원 필요</v>
+        <v/>
       </c>
       <c r="F61" s="2" t="str">
         <v/>
@@ -2232,7 +2232,7 @@
         <v>75</v>
       </c>
       <c r="E62" s="2" t="str">
-        <v>원만</v>
+        <v/>
       </c>
       <c r="F62" s="2" t="str">
         <v/>
@@ -2261,7 +2261,7 @@
         <v>86</v>
       </c>
       <c r="E63" s="2" t="str">
-        <v>원만</v>
+        <v/>
       </c>
       <c r="F63" s="2" t="str">
         <v/>
@@ -2290,7 +2290,7 @@
         <v>64</v>
       </c>
       <c r="E64" s="2" t="str">
-        <v>원만</v>
+        <v>✓</v>
       </c>
       <c r="F64" s="2" t="str">
         <v/>
@@ -2319,7 +2319,7 @@
         <v>91</v>
       </c>
       <c r="E65" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F65" s="2" t="str">
         <v/>
@@ -2348,7 +2348,7 @@
         <v>67</v>
       </c>
       <c r="E66" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F66" s="2" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>78</v>
       </c>
       <c r="E67" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F67" s="2" t="str">
         <v/>
@@ -2406,7 +2406,7 @@
         <v>85</v>
       </c>
       <c r="E68" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F68" s="2" t="str">
         <v/>
@@ -2435,7 +2435,7 @@
         <v>84</v>
       </c>
       <c r="E69" s="2" t="str">
-        <v>원만</v>
+        <v>✓</v>
       </c>
       <c r="F69" s="2" t="str">
         <v/>
@@ -2464,7 +2464,7 @@
         <v>83</v>
       </c>
       <c r="E70" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F70" s="2" t="str">
         <v/>
@@ -2493,7 +2493,7 @@
         <v>77</v>
       </c>
       <c r="E71" s="2" t="str">
-        <v>원만</v>
+        <v/>
       </c>
       <c r="F71" s="2" t="str">
         <v/>
@@ -2522,7 +2522,7 @@
         <v>77</v>
       </c>
       <c r="E72" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F72" s="2" t="str">
         <v/>
@@ -2551,7 +2551,7 @@
         <v>73</v>
       </c>
       <c r="E73" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F73" s="2" t="str">
         <v>✓</v>
@@ -2580,7 +2580,7 @@
         <v>88</v>
       </c>
       <c r="E74" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F74" s="2" t="str">
         <v/>
@@ -2609,7 +2609,7 @@
         <v>89</v>
       </c>
       <c r="E75" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F75" s="2" t="str">
         <v/>
@@ -2638,7 +2638,7 @@
         <v>79</v>
       </c>
       <c r="E76" s="2" t="str">
-        <v>지원 필요</v>
+        <v/>
       </c>
       <c r="F76" s="2" t="str">
         <v/>
@@ -2667,7 +2667,7 @@
         <v>73</v>
       </c>
       <c r="E77" s="2" t="str">
-        <v>원만</v>
+        <v/>
       </c>
       <c r="F77" s="2" t="str">
         <v/>
@@ -2696,7 +2696,7 @@
         <v>72</v>
       </c>
       <c r="E78" s="2" t="str">
-        <v>보통</v>
+        <v/>
       </c>
       <c r="F78" s="2" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>82</v>
       </c>
       <c r="E79" s="2" t="str">
-        <v>원만</v>
+        <v/>
       </c>
       <c r="F79" s="2" t="str">
         <v/>
@@ -2754,7 +2754,7 @@
         <v>78</v>
       </c>
       <c r="E80" s="2" t="str">
-        <v>원만</v>
+        <v>✓</v>
       </c>
       <c r="F80" s="2" t="str">
         <v/>
@@ -2783,7 +2783,7 @@
         <v>83</v>
       </c>
       <c r="E81" s="2" t="str">
-        <v>지원 필요</v>
+        <v/>
       </c>
       <c r="F81" s="2" t="str">
         <v/>
@@ -2812,7 +2812,7 @@
         <v>64</v>
       </c>
       <c r="E82" s="2" t="str">
-        <v>원만</v>
+        <v/>
       </c>
       <c r="F82" s="2" t="str">
         <v/>

--- a/public/samples/ko/sample1.xlsx
+++ b/public/samples/ko/sample1.xlsx
@@ -492,10 +492,10 @@
         <v>학업 성취도</v>
       </c>
       <c r="E2" s="2" t="str">
-        <v>교우 관계 지원</v>
+        <v>수학 수준</v>
       </c>
       <c r="F2" s="2" t="str">
-        <v>특수교육 대상</v>
+        <v>학습 지원</v>
       </c>
       <c r="G2" s="2" t="str">
         <v>한국어 지원</v>
@@ -520,8 +520,8 @@
       <c r="D3" s="2">
         <v>73</v>
       </c>
-      <c r="E3" s="2" t="str">
-        <v/>
+      <c r="E3" s="2">
+        <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
         <v/>
@@ -549,8 +549,8 @@
       <c r="D4" s="2">
         <v>67</v>
       </c>
-      <c r="E4" s="2" t="str">
-        <v/>
+      <c r="E4" s="2">
+        <v>2</v>
       </c>
       <c r="F4" s="2" t="str">
         <v/>
@@ -578,8 +578,8 @@
       <c r="D5" s="2">
         <v>79</v>
       </c>
-      <c r="E5" s="2" t="str">
-        <v/>
+      <c r="E5" s="2">
+        <v>3</v>
       </c>
       <c r="F5" s="2" t="str">
         <v/>
@@ -607,8 +607,8 @@
       <c r="D6" s="2">
         <v>72</v>
       </c>
-      <c r="E6" s="2" t="str">
-        <v/>
+      <c r="E6" s="2">
+        <v>4</v>
       </c>
       <c r="F6" s="2" t="str">
         <v/>
@@ -636,8 +636,8 @@
       <c r="D7" s="2">
         <v>78</v>
       </c>
-      <c r="E7" s="2" t="str">
-        <v/>
+      <c r="E7" s="2">
+        <v>3</v>
       </c>
       <c r="F7" s="2" t="str">
         <v/>
@@ -665,8 +665,8 @@
       <c r="D8" s="2">
         <v>68</v>
       </c>
-      <c r="E8" s="2" t="str">
-        <v/>
+      <c r="E8" s="2">
+        <v>2</v>
       </c>
       <c r="F8" s="2" t="str">
         <v/>
@@ -694,8 +694,8 @@
       <c r="D9" s="2">
         <v>77</v>
       </c>
-      <c r="E9" s="2" t="str">
-        <v/>
+      <c r="E9" s="2">
+        <v>5</v>
       </c>
       <c r="F9" s="2" t="str">
         <v/>
@@ -723,8 +723,8 @@
       <c r="D10" s="2">
         <v>83</v>
       </c>
-      <c r="E10" s="2" t="str">
-        <v>✓</v>
+      <c r="E10" s="2">
+        <v>2</v>
       </c>
       <c r="F10" s="2" t="str">
         <v>✓</v>
@@ -752,8 +752,8 @@
       <c r="D11" s="2">
         <v>86</v>
       </c>
-      <c r="E11" s="2" t="str">
-        <v/>
+      <c r="E11" s="2">
+        <v>2</v>
       </c>
       <c r="F11" s="2" t="str">
         <v/>
@@ -781,8 +781,8 @@
       <c r="D12" s="2">
         <v>71</v>
       </c>
-      <c r="E12" s="2" t="str">
-        <v/>
+      <c r="E12" s="2">
+        <v>4</v>
       </c>
       <c r="F12" s="2" t="str">
         <v/>
@@ -810,8 +810,8 @@
       <c r="D13" s="2">
         <v>75</v>
       </c>
-      <c r="E13" s="2" t="str">
-        <v>✓</v>
+      <c r="E13" s="2">
+        <v>1</v>
       </c>
       <c r="F13" s="2" t="str">
         <v/>
@@ -839,8 +839,8 @@
       <c r="D14" s="2">
         <v>88</v>
       </c>
-      <c r="E14" s="2" t="str">
-        <v/>
+      <c r="E14" s="2">
+        <v>4</v>
       </c>
       <c r="F14" s="2" t="str">
         <v>✓</v>
@@ -868,8 +868,8 @@
       <c r="D15" s="2">
         <v>76</v>
       </c>
-      <c r="E15" s="2" t="str">
-        <v/>
+      <c r="E15" s="2">
+        <v>4</v>
       </c>
       <c r="F15" s="2" t="str">
         <v/>
@@ -897,8 +897,8 @@
       <c r="D16" s="2">
         <v>70</v>
       </c>
-      <c r="E16" s="2" t="str">
-        <v/>
+      <c r="E16" s="2">
+        <v>3</v>
       </c>
       <c r="F16" s="2" t="str">
         <v>✓</v>
@@ -926,8 +926,8 @@
       <c r="D17" s="2">
         <v>73</v>
       </c>
-      <c r="E17" s="2" t="str">
-        <v>✓</v>
+      <c r="E17" s="2">
+        <v>1</v>
       </c>
       <c r="F17" s="2" t="str">
         <v>✓</v>
@@ -955,8 +955,8 @@
       <c r="D18" s="2">
         <v>88</v>
       </c>
-      <c r="E18" s="2" t="str">
-        <v/>
+      <c r="E18" s="2">
+        <v>3</v>
       </c>
       <c r="F18" s="2" t="str">
         <v/>
@@ -984,8 +984,8 @@
       <c r="D19" s="2">
         <v>72</v>
       </c>
-      <c r="E19" s="2" t="str">
-        <v/>
+      <c r="E19" s="2">
+        <v>3</v>
       </c>
       <c r="F19" s="2" t="str">
         <v/>
@@ -1013,8 +1013,8 @@
       <c r="D20" s="2">
         <v>74</v>
       </c>
-      <c r="E20" s="2" t="str">
-        <v/>
+      <c r="E20" s="2">
+        <v>2</v>
       </c>
       <c r="F20" s="2" t="str">
         <v/>
@@ -1042,8 +1042,8 @@
       <c r="D21" s="2">
         <v>82</v>
       </c>
-      <c r="E21" s="2" t="str">
-        <v/>
+      <c r="E21" s="2">
+        <v>3</v>
       </c>
       <c r="F21" s="2" t="str">
         <v/>
@@ -1071,8 +1071,8 @@
       <c r="D22" s="2">
         <v>84</v>
       </c>
-      <c r="E22" s="2" t="str">
-        <v/>
+      <c r="E22" s="2">
+        <v>2</v>
       </c>
       <c r="F22" s="2" t="str">
         <v/>
@@ -1100,8 +1100,8 @@
       <c r="D23" s="2">
         <v>71</v>
       </c>
-      <c r="E23" s="2" t="str">
-        <v/>
+      <c r="E23" s="2">
+        <v>2</v>
       </c>
       <c r="F23" s="2" t="str">
         <v/>
@@ -1129,8 +1129,8 @@
       <c r="D24" s="2">
         <v>80</v>
       </c>
-      <c r="E24" s="2" t="str">
-        <v/>
+      <c r="E24" s="2">
+        <v>3</v>
       </c>
       <c r="F24" s="2" t="str">
         <v/>
@@ -1158,8 +1158,8 @@
       <c r="D25" s="2">
         <v>75</v>
       </c>
-      <c r="E25" s="2" t="str">
-        <v/>
+      <c r="E25" s="2">
+        <v>3</v>
       </c>
       <c r="F25" s="2" t="str">
         <v/>
@@ -1187,8 +1187,8 @@
       <c r="D26" s="2">
         <v>85</v>
       </c>
-      <c r="E26" s="2" t="str">
-        <v/>
+      <c r="E26" s="2">
+        <v>3</v>
       </c>
       <c r="F26" s="2" t="str">
         <v/>
@@ -1216,8 +1216,8 @@
       <c r="D27" s="2">
         <v>94</v>
       </c>
-      <c r="E27" s="2" t="str">
-        <v/>
+      <c r="E27" s="2">
+        <v>4</v>
       </c>
       <c r="F27" s="2" t="str">
         <v/>
@@ -1245,8 +1245,8 @@
       <c r="D28" s="2">
         <v>83</v>
       </c>
-      <c r="E28" s="2" t="str">
-        <v/>
+      <c r="E28" s="2">
+        <v>5</v>
       </c>
       <c r="F28" s="2" t="str">
         <v/>
@@ -1274,8 +1274,8 @@
       <c r="D29" s="2">
         <v>78</v>
       </c>
-      <c r="E29" s="2" t="str">
-        <v/>
+      <c r="E29" s="2">
+        <v>5</v>
       </c>
       <c r="F29" s="2" t="str">
         <v>✓</v>
@@ -1303,8 +1303,8 @@
       <c r="D30" s="2">
         <v>84</v>
       </c>
-      <c r="E30" s="2" t="str">
-        <v/>
+      <c r="E30" s="2">
+        <v>3</v>
       </c>
       <c r="F30" s="2" t="str">
         <v/>
@@ -1332,8 +1332,8 @@
       <c r="D31" s="2">
         <v>62</v>
       </c>
-      <c r="E31" s="2" t="str">
-        <v/>
+      <c r="E31" s="2">
+        <v>3</v>
       </c>
       <c r="F31" s="2" t="str">
         <v/>
@@ -1361,8 +1361,8 @@
       <c r="D32" s="2">
         <v>75</v>
       </c>
-      <c r="E32" s="2" t="str">
-        <v/>
+      <c r="E32" s="2">
+        <v>5</v>
       </c>
       <c r="F32" s="2" t="str">
         <v/>
@@ -1390,8 +1390,8 @@
       <c r="D33" s="2">
         <v>71</v>
       </c>
-      <c r="E33" s="2" t="str">
-        <v/>
+      <c r="E33" s="2">
+        <v>2</v>
       </c>
       <c r="F33" s="2" t="str">
         <v/>
@@ -1419,8 +1419,8 @@
       <c r="D34" s="2">
         <v>84</v>
       </c>
-      <c r="E34" s="2" t="str">
-        <v/>
+      <c r="E34" s="2">
+        <v>3</v>
       </c>
       <c r="F34" s="2" t="str">
         <v/>
@@ -1448,8 +1448,8 @@
       <c r="D35" s="2">
         <v>72</v>
       </c>
-      <c r="E35" s="2" t="str">
-        <v/>
+      <c r="E35" s="2">
+        <v>2</v>
       </c>
       <c r="F35" s="2" t="str">
         <v/>
@@ -1477,8 +1477,8 @@
       <c r="D36" s="2">
         <v>64</v>
       </c>
-      <c r="E36" s="2" t="str">
-        <v/>
+      <c r="E36" s="2">
+        <v>4</v>
       </c>
       <c r="F36" s="2" t="str">
         <v/>
@@ -1506,8 +1506,8 @@
       <c r="D37" s="2">
         <v>65</v>
       </c>
-      <c r="E37" s="2" t="str">
-        <v/>
+      <c r="E37" s="2">
+        <v>2</v>
       </c>
       <c r="F37" s="2" t="str">
         <v>✓</v>
@@ -1535,8 +1535,8 @@
       <c r="D38" s="2">
         <v>74</v>
       </c>
-      <c r="E38" s="2" t="str">
-        <v/>
+      <c r="E38" s="2">
+        <v>3</v>
       </c>
       <c r="F38" s="2" t="str">
         <v/>
@@ -1564,8 +1564,8 @@
       <c r="D39" s="2">
         <v>73</v>
       </c>
-      <c r="E39" s="2" t="str">
-        <v/>
+      <c r="E39" s="2">
+        <v>3</v>
       </c>
       <c r="F39" s="2" t="str">
         <v/>
@@ -1593,8 +1593,8 @@
       <c r="D40" s="2">
         <v>78</v>
       </c>
-      <c r="E40" s="2" t="str">
-        <v/>
+      <c r="E40" s="2">
+        <v>4</v>
       </c>
       <c r="F40" s="2" t="str">
         <v/>
@@ -1622,8 +1622,8 @@
       <c r="D41" s="2">
         <v>67</v>
       </c>
-      <c r="E41" s="2" t="str">
-        <v>✓</v>
+      <c r="E41" s="2">
+        <v>1</v>
       </c>
       <c r="F41" s="2" t="str">
         <v/>
@@ -1651,8 +1651,8 @@
       <c r="D42" s="2">
         <v>73</v>
       </c>
-      <c r="E42" s="2" t="str">
-        <v/>
+      <c r="E42" s="2">
+        <v>2</v>
       </c>
       <c r="F42" s="2" t="str">
         <v/>
@@ -1680,8 +1680,8 @@
       <c r="D43" s="2">
         <v>81</v>
       </c>
-      <c r="E43" s="2" t="str">
-        <v/>
+      <c r="E43" s="2">
+        <v>4</v>
       </c>
       <c r="F43" s="2" t="str">
         <v/>
@@ -1709,8 +1709,8 @@
       <c r="D44" s="2">
         <v>79</v>
       </c>
-      <c r="E44" s="2" t="str">
-        <v/>
+      <c r="E44" s="2">
+        <v>4</v>
       </c>
       <c r="F44" s="2" t="str">
         <v/>
@@ -1738,8 +1738,8 @@
       <c r="D45" s="2">
         <v>81</v>
       </c>
-      <c r="E45" s="2" t="str">
-        <v/>
+      <c r="E45" s="2">
+        <v>5</v>
       </c>
       <c r="F45" s="2" t="str">
         <v/>
@@ -1767,8 +1767,8 @@
       <c r="D46" s="2">
         <v>81</v>
       </c>
-      <c r="E46" s="2" t="str">
-        <v/>
+      <c r="E46" s="2">
+        <v>3</v>
       </c>
       <c r="F46" s="2" t="str">
         <v/>
@@ -1796,8 +1796,8 @@
       <c r="D47" s="2">
         <v>89</v>
       </c>
-      <c r="E47" s="2" t="str">
-        <v/>
+      <c r="E47" s="2">
+        <v>2</v>
       </c>
       <c r="F47" s="2" t="str">
         <v/>
@@ -1825,8 +1825,8 @@
       <c r="D48" s="2">
         <v>74</v>
       </c>
-      <c r="E48" s="2" t="str">
-        <v/>
+      <c r="E48" s="2">
+        <v>3</v>
       </c>
       <c r="F48" s="2" t="str">
         <v/>
@@ -1854,8 +1854,8 @@
       <c r="D49" s="2">
         <v>81</v>
       </c>
-      <c r="E49" s="2" t="str">
-        <v/>
+      <c r="E49" s="2">
+        <v>5</v>
       </c>
       <c r="F49" s="2" t="str">
         <v/>
@@ -1883,8 +1883,8 @@
       <c r="D50" s="2">
         <v>80</v>
       </c>
-      <c r="E50" s="2" t="str">
-        <v/>
+      <c r="E50" s="2">
+        <v>3</v>
       </c>
       <c r="F50" s="2" t="str">
         <v/>
@@ -1912,8 +1912,8 @@
       <c r="D51" s="2">
         <v>78</v>
       </c>
-      <c r="E51" s="2" t="str">
-        <v/>
+      <c r="E51" s="2">
+        <v>2</v>
       </c>
       <c r="F51" s="2" t="str">
         <v/>
@@ -1941,8 +1941,8 @@
       <c r="D52" s="2">
         <v>93</v>
       </c>
-      <c r="E52" s="2" t="str">
-        <v/>
+      <c r="E52" s="2">
+        <v>3</v>
       </c>
       <c r="F52" s="2" t="str">
         <v>✓</v>
@@ -1970,8 +1970,8 @@
       <c r="D53" s="2">
         <v>64</v>
       </c>
-      <c r="E53" s="2" t="str">
-        <v/>
+      <c r="E53" s="2">
+        <v>4</v>
       </c>
       <c r="F53" s="2" t="str">
         <v/>
@@ -1999,8 +1999,8 @@
       <c r="D54" s="2">
         <v>79</v>
       </c>
-      <c r="E54" s="2" t="str">
-        <v/>
+      <c r="E54" s="2">
+        <v>3</v>
       </c>
       <c r="F54" s="2" t="str">
         <v>✓</v>
@@ -2028,8 +2028,8 @@
       <c r="D55" s="2">
         <v>75</v>
       </c>
-      <c r="E55" s="2" t="str">
-        <v/>
+      <c r="E55" s="2">
+        <v>4</v>
       </c>
       <c r="F55" s="2" t="str">
         <v/>
@@ -2057,8 +2057,8 @@
       <c r="D56" s="2">
         <v>84</v>
       </c>
-      <c r="E56" s="2" t="str">
-        <v/>
+      <c r="E56" s="2">
+        <v>4</v>
       </c>
       <c r="F56" s="2" t="str">
         <v/>
@@ -2086,8 +2086,8 @@
       <c r="D57" s="2">
         <v>78</v>
       </c>
-      <c r="E57" s="2" t="str">
-        <v/>
+      <c r="E57" s="2">
+        <v>3</v>
       </c>
       <c r="F57" s="2" t="str">
         <v/>
@@ -2115,8 +2115,8 @@
       <c r="D58" s="2">
         <v>82</v>
       </c>
-      <c r="E58" s="2" t="str">
-        <v/>
+      <c r="E58" s="2">
+        <v>3</v>
       </c>
       <c r="F58" s="2" t="str">
         <v/>
@@ -2144,8 +2144,8 @@
       <c r="D59" s="2">
         <v>93</v>
       </c>
-      <c r="E59" s="2" t="str">
-        <v>✓</v>
+      <c r="E59" s="2">
+        <v>1</v>
       </c>
       <c r="F59" s="2" t="str">
         <v/>
@@ -2173,8 +2173,8 @@
       <c r="D60" s="2">
         <v>87</v>
       </c>
-      <c r="E60" s="2" t="str">
-        <v/>
+      <c r="E60" s="2">
+        <v>5</v>
       </c>
       <c r="F60" s="2" t="str">
         <v/>
@@ -2202,8 +2202,8 @@
       <c r="D61" s="2">
         <v>72</v>
       </c>
-      <c r="E61" s="2" t="str">
-        <v/>
+      <c r="E61" s="2">
+        <v>5</v>
       </c>
       <c r="F61" s="2" t="str">
         <v/>
@@ -2231,8 +2231,8 @@
       <c r="D62" s="2">
         <v>75</v>
       </c>
-      <c r="E62" s="2" t="str">
-        <v/>
+      <c r="E62" s="2">
+        <v>2</v>
       </c>
       <c r="F62" s="2" t="str">
         <v/>
@@ -2260,8 +2260,8 @@
       <c r="D63" s="2">
         <v>86</v>
       </c>
-      <c r="E63" s="2" t="str">
-        <v/>
+      <c r="E63" s="2">
+        <v>2</v>
       </c>
       <c r="F63" s="2" t="str">
         <v/>
@@ -2289,8 +2289,8 @@
       <c r="D64" s="2">
         <v>64</v>
       </c>
-      <c r="E64" s="2" t="str">
-        <v>✓</v>
+      <c r="E64" s="2">
+        <v>1</v>
       </c>
       <c r="F64" s="2" t="str">
         <v/>
@@ -2318,8 +2318,8 @@
       <c r="D65" s="2">
         <v>91</v>
       </c>
-      <c r="E65" s="2" t="str">
-        <v/>
+      <c r="E65" s="2">
+        <v>3</v>
       </c>
       <c r="F65" s="2" t="str">
         <v/>
@@ -2347,8 +2347,8 @@
       <c r="D66" s="2">
         <v>67</v>
       </c>
-      <c r="E66" s="2" t="str">
-        <v/>
+      <c r="E66" s="2">
+        <v>3</v>
       </c>
       <c r="F66" s="2" t="str">
         <v/>
@@ -2376,8 +2376,8 @@
       <c r="D67" s="2">
         <v>78</v>
       </c>
-      <c r="E67" s="2" t="str">
-        <v/>
+      <c r="E67" s="2">
+        <v>3</v>
       </c>
       <c r="F67" s="2" t="str">
         <v/>
@@ -2405,8 +2405,8 @@
       <c r="D68" s="2">
         <v>85</v>
       </c>
-      <c r="E68" s="2" t="str">
-        <v/>
+      <c r="E68" s="2">
+        <v>3</v>
       </c>
       <c r="F68" s="2" t="str">
         <v/>
@@ -2434,8 +2434,8 @@
       <c r="D69" s="2">
         <v>84</v>
       </c>
-      <c r="E69" s="2" t="str">
-        <v>✓</v>
+      <c r="E69" s="2">
+        <v>1</v>
       </c>
       <c r="F69" s="2" t="str">
         <v/>
@@ -2463,8 +2463,8 @@
       <c r="D70" s="2">
         <v>83</v>
       </c>
-      <c r="E70" s="2" t="str">
-        <v/>
+      <c r="E70" s="2">
+        <v>3</v>
       </c>
       <c r="F70" s="2" t="str">
         <v/>
@@ -2492,8 +2492,8 @@
       <c r="D71" s="2">
         <v>77</v>
       </c>
-      <c r="E71" s="2" t="str">
-        <v/>
+      <c r="E71" s="2">
+        <v>2</v>
       </c>
       <c r="F71" s="2" t="str">
         <v/>
@@ -2521,8 +2521,8 @@
       <c r="D72" s="2">
         <v>77</v>
       </c>
-      <c r="E72" s="2" t="str">
-        <v/>
+      <c r="E72" s="2">
+        <v>3</v>
       </c>
       <c r="F72" s="2" t="str">
         <v/>
@@ -2550,8 +2550,8 @@
       <c r="D73" s="2">
         <v>73</v>
       </c>
-      <c r="E73" s="2" t="str">
-        <v/>
+      <c r="E73" s="2">
+        <v>3</v>
       </c>
       <c r="F73" s="2" t="str">
         <v>✓</v>
@@ -2579,8 +2579,8 @@
       <c r="D74" s="2">
         <v>88</v>
       </c>
-      <c r="E74" s="2" t="str">
-        <v/>
+      <c r="E74" s="2">
+        <v>4</v>
       </c>
       <c r="F74" s="2" t="str">
         <v/>
@@ -2608,8 +2608,8 @@
       <c r="D75" s="2">
         <v>89</v>
       </c>
-      <c r="E75" s="2" t="str">
-        <v/>
+      <c r="E75" s="2">
+        <v>3</v>
       </c>
       <c r="F75" s="2" t="str">
         <v/>
@@ -2637,8 +2637,8 @@
       <c r="D76" s="2">
         <v>79</v>
       </c>
-      <c r="E76" s="2" t="str">
-        <v/>
+      <c r="E76" s="2">
+        <v>5</v>
       </c>
       <c r="F76" s="2" t="str">
         <v/>
@@ -2666,8 +2666,8 @@
       <c r="D77" s="2">
         <v>73</v>
       </c>
-      <c r="E77" s="2" t="str">
-        <v/>
+      <c r="E77" s="2">
+        <v>2</v>
       </c>
       <c r="F77" s="2" t="str">
         <v/>
@@ -2695,8 +2695,8 @@
       <c r="D78" s="2">
         <v>72</v>
       </c>
-      <c r="E78" s="2" t="str">
-        <v/>
+      <c r="E78" s="2">
+        <v>4</v>
       </c>
       <c r="F78" s="2" t="str">
         <v/>
@@ -2724,8 +2724,8 @@
       <c r="D79" s="2">
         <v>82</v>
       </c>
-      <c r="E79" s="2" t="str">
-        <v/>
+      <c r="E79" s="2">
+        <v>2</v>
       </c>
       <c r="F79" s="2" t="str">
         <v/>
@@ -2753,8 +2753,8 @@
       <c r="D80" s="2">
         <v>78</v>
       </c>
-      <c r="E80" s="2" t="str">
-        <v>✓</v>
+      <c r="E80" s="2">
+        <v>1</v>
       </c>
       <c r="F80" s="2" t="str">
         <v/>
@@ -2782,8 +2782,8 @@
       <c r="D81" s="2">
         <v>83</v>
       </c>
-      <c r="E81" s="2" t="str">
-        <v/>
+      <c r="E81" s="2">
+        <v>5</v>
       </c>
       <c r="F81" s="2" t="str">
         <v/>
@@ -2811,8 +2811,8 @@
       <c r="D82" s="2">
         <v>64</v>
       </c>
-      <c r="E82" s="2" t="str">
-        <v/>
+      <c r="E82" s="2">
+        <v>3</v>
       </c>
       <c r="F82" s="2" t="str">
         <v/>

--- a/public/samples/ko/sample1.xlsx
+++ b/public/samples/ko/sample1.xlsx
@@ -7,6 +7,7 @@
     <sheet name="학생 명단" sheetId="2" r:id="rId2"/>
     <sheet name="같은 반 배정" sheetId="3" r:id="rId3"/>
     <sheet name="분리 배정" sheetId="4" r:id="rId4"/>
+    <sheet name="항목" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -2924,4 +2925,100 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F8"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="str">
+        <v>항목</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>종류</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <v>선택지</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="str">
+        <v>성별</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <v>목록</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <v>남</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <v>여</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="str">
+        <v>학업 성취도</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <v>숫자</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="str">
+        <v>수학 수준</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <v>정도</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="str">
+        <v>학습 지원</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <v>체크</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="str">
+        <v>한국어 지원</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <v>체크</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="str">
+        <v>리더십</v>
+      </c>
+      <c r="B7" s="2" t="str">
+        <v>체크</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="str">
+        <v>출신 초등학교</v>
+      </c>
+      <c r="B8" s="2" t="str">
+        <v>목록</v>
+      </c>
+      <c r="C8" s="2" t="str">
+        <v>가람초</v>
+      </c>
+      <c r="D8" s="2" t="str">
+        <v>나래초</v>
+      </c>
+      <c r="E8" s="2" t="str">
+        <v>다솜초</v>
+      </c>
+      <c r="F8" s="2" t="str">
+        <v>라온초</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F8"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/public/samples/ko/sample1.xlsx
+++ b/public/samples/ko/sample1.xlsx
@@ -7,6 +7,7 @@
     <sheet name="학생 명단" sheetId="2" r:id="rId2"/>
     <sheet name="같은 반 배정" sheetId="3" r:id="rId3"/>
     <sheet name="분리 배정" sheetId="4" r:id="rId4"/>
+    <sheet name="항목" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -492,10 +493,10 @@
         <v>학업 성취도</v>
       </c>
       <c r="E2" s="2" t="str">
-        <v>교우 관계 지원</v>
+        <v>수학 수준</v>
       </c>
       <c r="F2" s="2" t="str">
-        <v>특수교육 대상</v>
+        <v>학습 지원</v>
       </c>
       <c r="G2" s="2" t="str">
         <v>한국어 지원</v>
@@ -520,8 +521,8 @@
       <c r="D3" s="2">
         <v>73</v>
       </c>
-      <c r="E3" s="2" t="str">
-        <v/>
+      <c r="E3" s="2">
+        <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
         <v/>
@@ -549,8 +550,8 @@
       <c r="D4" s="2">
         <v>67</v>
       </c>
-      <c r="E4" s="2" t="str">
-        <v/>
+      <c r="E4" s="2">
+        <v>2</v>
       </c>
       <c r="F4" s="2" t="str">
         <v/>
@@ -578,8 +579,8 @@
       <c r="D5" s="2">
         <v>79</v>
       </c>
-      <c r="E5" s="2" t="str">
-        <v/>
+      <c r="E5" s="2">
+        <v>3</v>
       </c>
       <c r="F5" s="2" t="str">
         <v/>
@@ -607,8 +608,8 @@
       <c r="D6" s="2">
         <v>72</v>
       </c>
-      <c r="E6" s="2" t="str">
-        <v/>
+      <c r="E6" s="2">
+        <v>4</v>
       </c>
       <c r="F6" s="2" t="str">
         <v/>
@@ -636,8 +637,8 @@
       <c r="D7" s="2">
         <v>78</v>
       </c>
-      <c r="E7" s="2" t="str">
-        <v/>
+      <c r="E7" s="2">
+        <v>3</v>
       </c>
       <c r="F7" s="2" t="str">
         <v/>
@@ -665,8 +666,8 @@
       <c r="D8" s="2">
         <v>68</v>
       </c>
-      <c r="E8" s="2" t="str">
-        <v/>
+      <c r="E8" s="2">
+        <v>2</v>
       </c>
       <c r="F8" s="2" t="str">
         <v/>
@@ -694,8 +695,8 @@
       <c r="D9" s="2">
         <v>77</v>
       </c>
-      <c r="E9" s="2" t="str">
-        <v/>
+      <c r="E9" s="2">
+        <v>5</v>
       </c>
       <c r="F9" s="2" t="str">
         <v/>
@@ -723,8 +724,8 @@
       <c r="D10" s="2">
         <v>83</v>
       </c>
-      <c r="E10" s="2" t="str">
-        <v>✓</v>
+      <c r="E10" s="2">
+        <v>2</v>
       </c>
       <c r="F10" s="2" t="str">
         <v>✓</v>
@@ -752,8 +753,8 @@
       <c r="D11" s="2">
         <v>86</v>
       </c>
-      <c r="E11" s="2" t="str">
-        <v/>
+      <c r="E11" s="2">
+        <v>2</v>
       </c>
       <c r="F11" s="2" t="str">
         <v/>
@@ -781,8 +782,8 @@
       <c r="D12" s="2">
         <v>71</v>
       </c>
-      <c r="E12" s="2" t="str">
-        <v/>
+      <c r="E12" s="2">
+        <v>4</v>
       </c>
       <c r="F12" s="2" t="str">
         <v/>
@@ -810,8 +811,8 @@
       <c r="D13" s="2">
         <v>75</v>
       </c>
-      <c r="E13" s="2" t="str">
-        <v>✓</v>
+      <c r="E13" s="2">
+        <v>1</v>
       </c>
       <c r="F13" s="2" t="str">
         <v/>
@@ -839,8 +840,8 @@
       <c r="D14" s="2">
         <v>88</v>
       </c>
-      <c r="E14" s="2" t="str">
-        <v/>
+      <c r="E14" s="2">
+        <v>4</v>
       </c>
       <c r="F14" s="2" t="str">
         <v>✓</v>
@@ -868,8 +869,8 @@
       <c r="D15" s="2">
         <v>76</v>
       </c>
-      <c r="E15" s="2" t="str">
-        <v/>
+      <c r="E15" s="2">
+        <v>4</v>
       </c>
       <c r="F15" s="2" t="str">
         <v/>
@@ -897,8 +898,8 @@
       <c r="D16" s="2">
         <v>70</v>
       </c>
-      <c r="E16" s="2" t="str">
-        <v/>
+      <c r="E16" s="2">
+        <v>3</v>
       </c>
       <c r="F16" s="2" t="str">
         <v>✓</v>
@@ -926,8 +927,8 @@
       <c r="D17" s="2">
         <v>73</v>
       </c>
-      <c r="E17" s="2" t="str">
-        <v>✓</v>
+      <c r="E17" s="2">
+        <v>1</v>
       </c>
       <c r="F17" s="2" t="str">
         <v>✓</v>
@@ -955,8 +956,8 @@
       <c r="D18" s="2">
         <v>88</v>
       </c>
-      <c r="E18" s="2" t="str">
-        <v/>
+      <c r="E18" s="2">
+        <v>3</v>
       </c>
       <c r="F18" s="2" t="str">
         <v/>
@@ -984,8 +985,8 @@
       <c r="D19" s="2">
         <v>72</v>
       </c>
-      <c r="E19" s="2" t="str">
-        <v/>
+      <c r="E19" s="2">
+        <v>3</v>
       </c>
       <c r="F19" s="2" t="str">
         <v/>
@@ -1013,8 +1014,8 @@
       <c r="D20" s="2">
         <v>74</v>
       </c>
-      <c r="E20" s="2" t="str">
-        <v/>
+      <c r="E20" s="2">
+        <v>2</v>
       </c>
       <c r="F20" s="2" t="str">
         <v/>
@@ -1042,8 +1043,8 @@
       <c r="D21" s="2">
         <v>82</v>
       </c>
-      <c r="E21" s="2" t="str">
-        <v/>
+      <c r="E21" s="2">
+        <v>3</v>
       </c>
       <c r="F21" s="2" t="str">
         <v/>
@@ -1071,8 +1072,8 @@
       <c r="D22" s="2">
         <v>84</v>
       </c>
-      <c r="E22" s="2" t="str">
-        <v/>
+      <c r="E22" s="2">
+        <v>2</v>
       </c>
       <c r="F22" s="2" t="str">
         <v/>
@@ -1100,8 +1101,8 @@
       <c r="D23" s="2">
         <v>71</v>
       </c>
-      <c r="E23" s="2" t="str">
-        <v/>
+      <c r="E23" s="2">
+        <v>2</v>
       </c>
       <c r="F23" s="2" t="str">
         <v/>
@@ -1129,8 +1130,8 @@
       <c r="D24" s="2">
         <v>80</v>
       </c>
-      <c r="E24" s="2" t="str">
-        <v/>
+      <c r="E24" s="2">
+        <v>3</v>
       </c>
       <c r="F24" s="2" t="str">
         <v/>
@@ -1158,8 +1159,8 @@
       <c r="D25" s="2">
         <v>75</v>
       </c>
-      <c r="E25" s="2" t="str">
-        <v/>
+      <c r="E25" s="2">
+        <v>3</v>
       </c>
       <c r="F25" s="2" t="str">
         <v/>
@@ -1187,8 +1188,8 @@
       <c r="D26" s="2">
         <v>85</v>
       </c>
-      <c r="E26" s="2" t="str">
-        <v/>
+      <c r="E26" s="2">
+        <v>3</v>
       </c>
       <c r="F26" s="2" t="str">
         <v/>
@@ -1216,8 +1217,8 @@
       <c r="D27" s="2">
         <v>94</v>
       </c>
-      <c r="E27" s="2" t="str">
-        <v/>
+      <c r="E27" s="2">
+        <v>4</v>
       </c>
       <c r="F27" s="2" t="str">
         <v/>
@@ -1245,8 +1246,8 @@
       <c r="D28" s="2">
         <v>83</v>
       </c>
-      <c r="E28" s="2" t="str">
-        <v/>
+      <c r="E28" s="2">
+        <v>5</v>
       </c>
       <c r="F28" s="2" t="str">
         <v/>
@@ -1274,8 +1275,8 @@
       <c r="D29" s="2">
         <v>78</v>
       </c>
-      <c r="E29" s="2" t="str">
-        <v/>
+      <c r="E29" s="2">
+        <v>5</v>
       </c>
       <c r="F29" s="2" t="str">
         <v>✓</v>
@@ -1303,8 +1304,8 @@
       <c r="D30" s="2">
         <v>84</v>
       </c>
-      <c r="E30" s="2" t="str">
-        <v/>
+      <c r="E30" s="2">
+        <v>3</v>
       </c>
       <c r="F30" s="2" t="str">
         <v/>
@@ -1332,8 +1333,8 @@
       <c r="D31" s="2">
         <v>62</v>
       </c>
-      <c r="E31" s="2" t="str">
-        <v/>
+      <c r="E31" s="2">
+        <v>3</v>
       </c>
       <c r="F31" s="2" t="str">
         <v/>
@@ -1361,8 +1362,8 @@
       <c r="D32" s="2">
         <v>75</v>
       </c>
-      <c r="E32" s="2" t="str">
-        <v/>
+      <c r="E32" s="2">
+        <v>5</v>
       </c>
       <c r="F32" s="2" t="str">
         <v/>
@@ -1390,8 +1391,8 @@
       <c r="D33" s="2">
         <v>71</v>
       </c>
-      <c r="E33" s="2" t="str">
-        <v/>
+      <c r="E33" s="2">
+        <v>2</v>
       </c>
       <c r="F33" s="2" t="str">
         <v/>
@@ -1419,8 +1420,8 @@
       <c r="D34" s="2">
         <v>84</v>
       </c>
-      <c r="E34" s="2" t="str">
-        <v/>
+      <c r="E34" s="2">
+        <v>3</v>
       </c>
       <c r="F34" s="2" t="str">
         <v/>
@@ -1448,8 +1449,8 @@
       <c r="D35" s="2">
         <v>72</v>
       </c>
-      <c r="E35" s="2" t="str">
-        <v/>
+      <c r="E35" s="2">
+        <v>2</v>
       </c>
       <c r="F35" s="2" t="str">
         <v/>
@@ -1477,8 +1478,8 @@
       <c r="D36" s="2">
         <v>64</v>
       </c>
-      <c r="E36" s="2" t="str">
-        <v/>
+      <c r="E36" s="2">
+        <v>4</v>
       </c>
       <c r="F36" s="2" t="str">
         <v/>
@@ -1506,8 +1507,8 @@
       <c r="D37" s="2">
         <v>65</v>
       </c>
-      <c r="E37" s="2" t="str">
-        <v/>
+      <c r="E37" s="2">
+        <v>2</v>
       </c>
       <c r="F37" s="2" t="str">
         <v>✓</v>
@@ -1535,8 +1536,8 @@
       <c r="D38" s="2">
         <v>74</v>
       </c>
-      <c r="E38" s="2" t="str">
-        <v/>
+      <c r="E38" s="2">
+        <v>3</v>
       </c>
       <c r="F38" s="2" t="str">
         <v/>
@@ -1564,8 +1565,8 @@
       <c r="D39" s="2">
         <v>73</v>
       </c>
-      <c r="E39" s="2" t="str">
-        <v/>
+      <c r="E39" s="2">
+        <v>3</v>
       </c>
       <c r="F39" s="2" t="str">
         <v/>
@@ -1593,8 +1594,8 @@
       <c r="D40" s="2">
         <v>78</v>
       </c>
-      <c r="E40" s="2" t="str">
-        <v/>
+      <c r="E40" s="2">
+        <v>4</v>
       </c>
       <c r="F40" s="2" t="str">
         <v/>
@@ -1622,8 +1623,8 @@
       <c r="D41" s="2">
         <v>67</v>
       </c>
-      <c r="E41" s="2" t="str">
-        <v>✓</v>
+      <c r="E41" s="2">
+        <v>1</v>
       </c>
       <c r="F41" s="2" t="str">
         <v/>
@@ -1651,8 +1652,8 @@
       <c r="D42" s="2">
         <v>73</v>
       </c>
-      <c r="E42" s="2" t="str">
-        <v/>
+      <c r="E42" s="2">
+        <v>2</v>
       </c>
       <c r="F42" s="2" t="str">
         <v/>
@@ -1680,8 +1681,8 @@
       <c r="D43" s="2">
         <v>81</v>
       </c>
-      <c r="E43" s="2" t="str">
-        <v/>
+      <c r="E43" s="2">
+        <v>4</v>
       </c>
       <c r="F43" s="2" t="str">
         <v/>
@@ -1709,8 +1710,8 @@
       <c r="D44" s="2">
         <v>79</v>
       </c>
-      <c r="E44" s="2" t="str">
-        <v/>
+      <c r="E44" s="2">
+        <v>4</v>
       </c>
       <c r="F44" s="2" t="str">
         <v/>
@@ -1738,8 +1739,8 @@
       <c r="D45" s="2">
         <v>81</v>
       </c>
-      <c r="E45" s="2" t="str">
-        <v/>
+      <c r="E45" s="2">
+        <v>5</v>
       </c>
       <c r="F45" s="2" t="str">
         <v/>
@@ -1767,8 +1768,8 @@
       <c r="D46" s="2">
         <v>81</v>
       </c>
-      <c r="E46" s="2" t="str">
-        <v/>
+      <c r="E46" s="2">
+        <v>3</v>
       </c>
       <c r="F46" s="2" t="str">
         <v/>
@@ -1796,8 +1797,8 @@
       <c r="D47" s="2">
         <v>89</v>
       </c>
-      <c r="E47" s="2" t="str">
-        <v/>
+      <c r="E47" s="2">
+        <v>2</v>
       </c>
       <c r="F47" s="2" t="str">
         <v/>
@@ -1825,8 +1826,8 @@
       <c r="D48" s="2">
         <v>74</v>
       </c>
-      <c r="E48" s="2" t="str">
-        <v/>
+      <c r="E48" s="2">
+        <v>3</v>
       </c>
       <c r="F48" s="2" t="str">
         <v/>
@@ -1854,8 +1855,8 @@
       <c r="D49" s="2">
         <v>81</v>
       </c>
-      <c r="E49" s="2" t="str">
-        <v/>
+      <c r="E49" s="2">
+        <v>5</v>
       </c>
       <c r="F49" s="2" t="str">
         <v/>
@@ -1883,8 +1884,8 @@
       <c r="D50" s="2">
         <v>80</v>
       </c>
-      <c r="E50" s="2" t="str">
-        <v/>
+      <c r="E50" s="2">
+        <v>3</v>
       </c>
       <c r="F50" s="2" t="str">
         <v/>
@@ -1912,8 +1913,8 @@
       <c r="D51" s="2">
         <v>78</v>
       </c>
-      <c r="E51" s="2" t="str">
-        <v/>
+      <c r="E51" s="2">
+        <v>2</v>
       </c>
       <c r="F51" s="2" t="str">
         <v/>
@@ -1941,8 +1942,8 @@
       <c r="D52" s="2">
         <v>93</v>
       </c>
-      <c r="E52" s="2" t="str">
-        <v/>
+      <c r="E52" s="2">
+        <v>3</v>
       </c>
       <c r="F52" s="2" t="str">
         <v>✓</v>
@@ -1970,8 +1971,8 @@
       <c r="D53" s="2">
         <v>64</v>
       </c>
-      <c r="E53" s="2" t="str">
-        <v/>
+      <c r="E53" s="2">
+        <v>4</v>
       </c>
       <c r="F53" s="2" t="str">
         <v/>
@@ -1999,8 +2000,8 @@
       <c r="D54" s="2">
         <v>79</v>
       </c>
-      <c r="E54" s="2" t="str">
-        <v/>
+      <c r="E54" s="2">
+        <v>3</v>
       </c>
       <c r="F54" s="2" t="str">
         <v>✓</v>
@@ -2028,8 +2029,8 @@
       <c r="D55" s="2">
         <v>75</v>
       </c>
-      <c r="E55" s="2" t="str">
-        <v/>
+      <c r="E55" s="2">
+        <v>4</v>
       </c>
       <c r="F55" s="2" t="str">
         <v/>
@@ -2057,8 +2058,8 @@
       <c r="D56" s="2">
         <v>84</v>
       </c>
-      <c r="E56" s="2" t="str">
-        <v/>
+      <c r="E56" s="2">
+        <v>4</v>
       </c>
       <c r="F56" s="2" t="str">
         <v/>
@@ -2086,8 +2087,8 @@
       <c r="D57" s="2">
         <v>78</v>
       </c>
-      <c r="E57" s="2" t="str">
-        <v/>
+      <c r="E57" s="2">
+        <v>3</v>
       </c>
       <c r="F57" s="2" t="str">
         <v/>
@@ -2115,8 +2116,8 @@
       <c r="D58" s="2">
         <v>82</v>
       </c>
-      <c r="E58" s="2" t="str">
-        <v/>
+      <c r="E58" s="2">
+        <v>3</v>
       </c>
       <c r="F58" s="2" t="str">
         <v/>
@@ -2144,8 +2145,8 @@
       <c r="D59" s="2">
         <v>93</v>
       </c>
-      <c r="E59" s="2" t="str">
-        <v>✓</v>
+      <c r="E59" s="2">
+        <v>1</v>
       </c>
       <c r="F59" s="2" t="str">
         <v/>
@@ -2173,8 +2174,8 @@
       <c r="D60" s="2">
         <v>87</v>
       </c>
-      <c r="E60" s="2" t="str">
-        <v/>
+      <c r="E60" s="2">
+        <v>5</v>
       </c>
       <c r="F60" s="2" t="str">
         <v/>
@@ -2202,8 +2203,8 @@
       <c r="D61" s="2">
         <v>72</v>
       </c>
-      <c r="E61" s="2" t="str">
-        <v/>
+      <c r="E61" s="2">
+        <v>5</v>
       </c>
       <c r="F61" s="2" t="str">
         <v/>
@@ -2231,8 +2232,8 @@
       <c r="D62" s="2">
         <v>75</v>
       </c>
-      <c r="E62" s="2" t="str">
-        <v/>
+      <c r="E62" s="2">
+        <v>2</v>
       </c>
       <c r="F62" s="2" t="str">
         <v/>
@@ -2260,8 +2261,8 @@
       <c r="D63" s="2">
         <v>86</v>
       </c>
-      <c r="E63" s="2" t="str">
-        <v/>
+      <c r="E63" s="2">
+        <v>2</v>
       </c>
       <c r="F63" s="2" t="str">
         <v/>
@@ -2289,8 +2290,8 @@
       <c r="D64" s="2">
         <v>64</v>
       </c>
-      <c r="E64" s="2" t="str">
-        <v>✓</v>
+      <c r="E64" s="2">
+        <v>1</v>
       </c>
       <c r="F64" s="2" t="str">
         <v/>
@@ -2318,8 +2319,8 @@
       <c r="D65" s="2">
         <v>91</v>
       </c>
-      <c r="E65" s="2" t="str">
-        <v/>
+      <c r="E65" s="2">
+        <v>3</v>
       </c>
       <c r="F65" s="2" t="str">
         <v/>
@@ -2347,8 +2348,8 @@
       <c r="D66" s="2">
         <v>67</v>
       </c>
-      <c r="E66" s="2" t="str">
-        <v/>
+      <c r="E66" s="2">
+        <v>3</v>
       </c>
       <c r="F66" s="2" t="str">
         <v/>
@@ -2376,8 +2377,8 @@
       <c r="D67" s="2">
         <v>78</v>
       </c>
-      <c r="E67" s="2" t="str">
-        <v/>
+      <c r="E67" s="2">
+        <v>3</v>
       </c>
       <c r="F67" s="2" t="str">
         <v/>
@@ -2405,8 +2406,8 @@
       <c r="D68" s="2">
         <v>85</v>
       </c>
-      <c r="E68" s="2" t="str">
-        <v/>
+      <c r="E68" s="2">
+        <v>3</v>
       </c>
       <c r="F68" s="2" t="str">
         <v/>
@@ -2434,8 +2435,8 @@
       <c r="D69" s="2">
         <v>84</v>
       </c>
-      <c r="E69" s="2" t="str">
-        <v>✓</v>
+      <c r="E69" s="2">
+        <v>1</v>
       </c>
       <c r="F69" s="2" t="str">
         <v/>
@@ -2463,8 +2464,8 @@
       <c r="D70" s="2">
         <v>83</v>
       </c>
-      <c r="E70" s="2" t="str">
-        <v/>
+      <c r="E70" s="2">
+        <v>3</v>
       </c>
       <c r="F70" s="2" t="str">
         <v/>
@@ -2492,8 +2493,8 @@
       <c r="D71" s="2">
         <v>77</v>
       </c>
-      <c r="E71" s="2" t="str">
-        <v/>
+      <c r="E71" s="2">
+        <v>2</v>
       </c>
       <c r="F71" s="2" t="str">
         <v/>
@@ -2521,8 +2522,8 @@
       <c r="D72" s="2">
         <v>77</v>
       </c>
-      <c r="E72" s="2" t="str">
-        <v/>
+      <c r="E72" s="2">
+        <v>3</v>
       </c>
       <c r="F72" s="2" t="str">
         <v/>
@@ -2550,8 +2551,8 @@
       <c r="D73" s="2">
         <v>73</v>
       </c>
-      <c r="E73" s="2" t="str">
-        <v/>
+      <c r="E73" s="2">
+        <v>3</v>
       </c>
       <c r="F73" s="2" t="str">
         <v>✓</v>
@@ -2579,8 +2580,8 @@
       <c r="D74" s="2">
         <v>88</v>
       </c>
-      <c r="E74" s="2" t="str">
-        <v/>
+      <c r="E74" s="2">
+        <v>4</v>
       </c>
       <c r="F74" s="2" t="str">
         <v/>
@@ -2608,8 +2609,8 @@
       <c r="D75" s="2">
         <v>89</v>
       </c>
-      <c r="E75" s="2" t="str">
-        <v/>
+      <c r="E75" s="2">
+        <v>3</v>
       </c>
       <c r="F75" s="2" t="str">
         <v/>
@@ -2637,8 +2638,8 @@
       <c r="D76" s="2">
         <v>79</v>
       </c>
-      <c r="E76" s="2" t="str">
-        <v/>
+      <c r="E76" s="2">
+        <v>5</v>
       </c>
       <c r="F76" s="2" t="str">
         <v/>
@@ -2666,8 +2667,8 @@
       <c r="D77" s="2">
         <v>73</v>
       </c>
-      <c r="E77" s="2" t="str">
-        <v/>
+      <c r="E77" s="2">
+        <v>2</v>
       </c>
       <c r="F77" s="2" t="str">
         <v/>
@@ -2695,8 +2696,8 @@
       <c r="D78" s="2">
         <v>72</v>
       </c>
-      <c r="E78" s="2" t="str">
-        <v/>
+      <c r="E78" s="2">
+        <v>4</v>
       </c>
       <c r="F78" s="2" t="str">
         <v/>
@@ -2724,8 +2725,8 @@
       <c r="D79" s="2">
         <v>82</v>
       </c>
-      <c r="E79" s="2" t="str">
-        <v/>
+      <c r="E79" s="2">
+        <v>2</v>
       </c>
       <c r="F79" s="2" t="str">
         <v/>
@@ -2753,8 +2754,8 @@
       <c r="D80" s="2">
         <v>78</v>
       </c>
-      <c r="E80" s="2" t="str">
-        <v>✓</v>
+      <c r="E80" s="2">
+        <v>1</v>
       </c>
       <c r="F80" s="2" t="str">
         <v/>
@@ -2782,8 +2783,8 @@
       <c r="D81" s="2">
         <v>83</v>
       </c>
-      <c r="E81" s="2" t="str">
-        <v/>
+      <c r="E81" s="2">
+        <v>5</v>
       </c>
       <c r="F81" s="2" t="str">
         <v/>
@@ -2811,8 +2812,8 @@
       <c r="D82" s="2">
         <v>64</v>
       </c>
-      <c r="E82" s="2" t="str">
-        <v/>
+      <c r="E82" s="2">
+        <v>3</v>
       </c>
       <c r="F82" s="2" t="str">
         <v/>
@@ -2924,4 +2925,100 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F8"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="str">
+        <v>항목</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>종류</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <v>선택지</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="str">
+        <v>성별</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <v>목록</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <v>남</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <v>여</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="str">
+        <v>학업 성취도</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <v>숫자</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="str">
+        <v>수학 수준</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <v>정도</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="str">
+        <v>학습 지원</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <v>체크</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="str">
+        <v>한국어 지원</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <v>체크</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="str">
+        <v>리더십</v>
+      </c>
+      <c r="B7" s="2" t="str">
+        <v>체크</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="str">
+        <v>출신 초등학교</v>
+      </c>
+      <c r="B8" s="2" t="str">
+        <v>목록</v>
+      </c>
+      <c r="C8" s="2" t="str">
+        <v>가람초</v>
+      </c>
+      <c r="D8" s="2" t="str">
+        <v>나래초</v>
+      </c>
+      <c r="E8" s="2" t="str">
+        <v>다솜초</v>
+      </c>
+      <c r="F8" s="2" t="str">
+        <v>라온초</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F8"/>
+  </ignoredErrors>
+</worksheet>
 </file>